--- a/output/roomself_excel/8644.xlsx
+++ b/output/roomself_excel/8644.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113955</v>
+        <v>64167</v>
       </c>
       <c r="D2" t="n">
-        <v>2704</v>
+        <v>2048</v>
       </c>
       <c r="E2" t="n">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="F2" t="n">
-        <v>337</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20139</v>
+        <v>372621</v>
       </c>
       <c r="D3" t="n">
-        <v>1280</v>
+        <v>7160</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>864</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64167</v>
+        <v>113955</v>
       </c>
       <c r="D4" t="n">
-        <v>2048</v>
+        <v>2704</v>
       </c>
       <c r="E4" t="n">
-        <v>293</v>
+        <v>370</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>372621</v>
+        <v>90880</v>
       </c>
       <c r="D5" t="n">
-        <v>7160</v>
+        <v>2444</v>
       </c>
       <c r="E5" t="n">
-        <v>873</v>
+        <v>370</v>
       </c>
       <c r="F5" t="n">
-        <v>864</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90880</v>
+        <v>16068</v>
       </c>
       <c r="D6" t="n">
-        <v>2444</v>
+        <v>1036</v>
       </c>
       <c r="E6" t="n">
-        <v>370</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>272</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16068</v>
+        <v>30622</v>
       </c>
       <c r="D7" t="n">
-        <v>1036</v>
+        <v>1548</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30622</v>
+        <v>20139</v>
       </c>
       <c r="D8" t="n">
-        <v>1548</v>
+        <v>1280</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">

--- a/output/roomself_excel/8644.xlsx
+++ b/output/roomself_excel/8644.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2048</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>293</v>
       </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>7160</v>
       </c>
-      <c r="E3" t="n">
-        <v>864</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>684</v>
+        <v>1190</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>814</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2704</v>
       </c>
-      <c r="E4" t="n">
-        <v>370</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>337</v>
+        <v>355</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>321</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>2444</v>
       </c>
-      <c r="E5" t="n">
-        <v>370</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>272</v>
+        <v>256</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>355</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,20 @@
       <c r="D6" t="n">
         <v>1036</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>103</v>
       </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>1548</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>60</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>50</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1280</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>101</v>
       </c>
-      <c r="F8" t="n">
-        <v>16</v>
-      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +729,27 @@
       <c r="D9" t="n">
         <v>1208</v>
       </c>
-      <c r="E9" t="n">
-        <v>171</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>163</v>
+        <v>147</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>155</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
